--- a/ESERCIZIO_M2-2-3_dati.xlsx
+++ b/ESERCIZIO_M2-2-3_dati.xlsx
@@ -5,30 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giordana\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giordana\Desktop\SecondWeekExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1AA6BA-DF8D-4BC7-A88D-EDA44A035EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCA03A4-855A-4945-8964-10CF73A5C037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-3900" windowWidth="38620" windowHeight="21100" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-3900" windowWidth="38620" windowHeight="21100" tabRatio="887" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendite" sheetId="1" r:id="rId1"/>
     <sheet name="Tabella pivot Vendite" sheetId="4" r:id="rId2"/>
     <sheet name="Tabella Pivot Vendite2" sheetId="5" r:id="rId3"/>
     <sheet name="Performances" sheetId="2" r:id="rId4"/>
-    <sheet name="Prestazione medie dipartimento" sheetId="6" r:id="rId5"/>
-    <sheet name="Media prestastio Dip. &gt;4" sheetId="7" r:id="rId6"/>
-    <sheet name="Social Media" sheetId="3" r:id="rId7"/>
-    <sheet name="Social Media Categoria" sheetId="11" r:id="rId8"/>
-    <sheet name="Social media T.Pivot" sheetId="12" r:id="rId9"/>
+    <sheet name="Media prestastio Dip. &gt;4" sheetId="7" r:id="rId5"/>
+    <sheet name="Social Media" sheetId="3" r:id="rId6"/>
+    <sheet name="Social Media Categoria" sheetId="11" r:id="rId7"/>
+    <sheet name="Social media T.Pivot" sheetId="12" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Performances!$A$1:$D$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Social Media'!$A$1:$J$1006</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Social Media'!$A$1:$J$1006</definedName>
     <definedName name="COD_PRODOTTO">Vendite!$B$2:$B$1048576</definedName>
     <definedName name="Codice">#REF!</definedName>
     <definedName name="DANIELE">#REF!</definedName>
@@ -49,19 +48,17 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
-    <pivotCache cacheId="1" r:id="rId12"/>
-    <pivotCache cacheId="2" r:id="rId13"/>
-    <pivotCache cacheId="3" r:id="rId14"/>
+    <pivotCache cacheId="80" r:id="rId10"/>
+    <pivotCache cacheId="89" r:id="rId11"/>
+    <pivotCache cacheId="82" r:id="rId12"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
+        <x14:slicerCache r:id="rId13"/>
+        <x14:slicerCache r:id="rId14"/>
         <x14:slicerCache r:id="rId15"/>
         <x14:slicerCache r:id="rId16"/>
-        <x14:slicerCache r:id="rId17"/>
-        <x14:slicerCache r:id="rId18"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -86,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="139">
   <si>
     <t>CATEGORIA PRODOTTO</t>
   </si>
@@ -460,9 +457,6 @@
     <t>Etichette di colonna</t>
   </si>
   <si>
-    <t>Media di Valutazione delle Prestazioni</t>
-  </si>
-  <si>
     <t>Diifferenza performance in % anno rispetto anno precedente</t>
   </si>
   <si>
@@ -503,6 +497,9 @@
   </si>
   <si>
     <t>arte</t>
+  </si>
+  <si>
+    <t>Somma di Diff.Performance rispetto anno precedente</t>
   </si>
 </sst>
 </file>
@@ -636,7 +633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -716,637 +713,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -1388,6 +760,32 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
@@ -4694,611 +4092,6 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="107"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="7"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[ESERCIZIO_M2-2-3_dati.xlsx]Prestazione medie dipartimento!Tabella pivot42</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent5">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent5">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="it-IT"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Prestazione medie dipartimento'!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Totale</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent5">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent5">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="it-IT"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Prestazione medie dipartimento'!$A$4:$A$9</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Finanza</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>IT</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Marketing</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Risorse Umane</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Vendite</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Prestazione medie dipartimento'!$B$4:$B$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>4.5916666666666668</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.2583333333333337</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.5749999999999997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.8249999999999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.2250000000000005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-8B1F-4C48-BFEC-5670EDF5F0B1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="100"/>
-        <c:overlap val="-24"/>
-        <c:axId val="532983184"/>
-        <c:axId val="532982704"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="532983184"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="532982704"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="532982704"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="532983184"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:dTable>
-        <c:showHorzBorder val="1"/>
-        <c:showVertBorder val="1"/>
-        <c:showOutline val="1"/>
-        <c:showKeys val="1"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr rtl="0">
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
-          </a:p>
-        </c:txPr>
-      </c:dTable>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="it-IT"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="it-IT"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="105"/>
     </mc:Choice>
     <mc:Fallback>
@@ -5344,6 +4137,234 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent3"/>
@@ -5489,9 +4510,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Media prestastio Dip. &gt;4'!$A$4:$A$43</c:f>
+              <c:f>'Media prestastio Dip. &gt;4'!$A$4:$A$69</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="36"/>
+                <c:ptCount val="60"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>104</c:v>
@@ -5566,39 +4587,111 @@
                     <c:v>158</c:v>
                   </c:pt>
                   <c:pt idx="24">
+                    <c:v>105</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>110</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>115</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>120</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>125</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>130</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>135</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>140</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>145</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>150</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>155</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>160</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>102</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>107</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>112</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>117</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>122</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>127</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>132</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>137</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>142</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>147</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>152</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>157</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
                     <c:v>101</c:v>
                   </c:pt>
-                  <c:pt idx="25">
+                  <c:pt idx="49">
                     <c:v>106</c:v>
                   </c:pt>
-                  <c:pt idx="26">
+                  <c:pt idx="50">
                     <c:v>111</c:v>
                   </c:pt>
-                  <c:pt idx="27">
+                  <c:pt idx="51">
                     <c:v>116</c:v>
                   </c:pt>
-                  <c:pt idx="28">
+                  <c:pt idx="52">
                     <c:v>121</c:v>
                   </c:pt>
-                  <c:pt idx="29">
+                  <c:pt idx="53">
                     <c:v>126</c:v>
                   </c:pt>
-                  <c:pt idx="30">
+                  <c:pt idx="54">
                     <c:v>131</c:v>
                   </c:pt>
-                  <c:pt idx="31">
+                  <c:pt idx="55">
                     <c:v>136</c:v>
                   </c:pt>
-                  <c:pt idx="32">
+                  <c:pt idx="56">
                     <c:v>141</c:v>
                   </c:pt>
-                  <c:pt idx="33">
+                  <c:pt idx="57">
                     <c:v>146</c:v>
                   </c:pt>
-                  <c:pt idx="34">
+                  <c:pt idx="58">
                     <c:v>151</c:v>
                   </c:pt>
-                  <c:pt idx="35">
+                  <c:pt idx="59">
                     <c:v>156</c:v>
                   </c:pt>
                 </c:lvl>
@@ -5610,6 +4703,12 @@
                     <c:v>IT</c:v>
                   </c:pt>
                   <c:pt idx="24">
+                    <c:v>Marketing</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>Risorse Umane</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
                     <c:v>Vendite</c:v>
                   </c:pt>
                 </c:lvl>
@@ -5618,124 +4717,196 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Media prestastio Dip. &gt;4'!$B$4:$B$43</c:f>
+              <c:f>'Media prestastio Dip. &gt;4'!$B$4:$B$69</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="36"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>4.8</c:v>
+                  <c:v>-95.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.2</c:v>
+                  <c:v>-95.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7</c:v>
+                  <c:v>-95.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5999999999999996</c:v>
+                  <c:v>-95.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.5</c:v>
+                  <c:v>-95.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.4000000000000004</c:v>
+                  <c:v>-95.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.9000000000000004</c:v>
+                  <c:v>-95.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.8</c:v>
+                  <c:v>-95.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.7</c:v>
+                  <c:v>-95.3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.2</c:v>
+                  <c:v>-95.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.7</c:v>
+                  <c:v>-95.3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.5999999999999996</c:v>
+                  <c:v>-95.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.2</c:v>
+                  <c:v>-95.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.5</c:v>
+                  <c:v>-95.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.0999999999999996</c:v>
+                  <c:v>-95.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.4000000000000004</c:v>
+                  <c:v>-95.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.3</c:v>
+                  <c:v>-95.7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>-96</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.2</c:v>
+                  <c:v>-95.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.3</c:v>
+                  <c:v>-95.7</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.0999999999999996</c:v>
+                  <c:v>-95.9</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.5</c:v>
+                  <c:v>-95.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.0999999999999996</c:v>
+                  <c:v>-95.9</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.4000000000000004</c:v>
+                  <c:v>-95.6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.5</c:v>
+                  <c:v>-96.5</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4</c:v>
+                  <c:v>-96.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.3</c:v>
+                  <c:v>-96.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.2</c:v>
+                  <c:v>-96.4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.0999999999999996</c:v>
+                  <c:v>-96.3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.9</c:v>
+                  <c:v>-96.2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4.5999999999999996</c:v>
+                  <c:v>-96.7</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4.4000000000000004</c:v>
+                  <c:v>-96.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4</c:v>
+                  <c:v>-96.6</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4.2</c:v>
+                  <c:v>-96.2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.3</c:v>
+                  <c:v>-96.6</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.2</c:v>
+                  <c:v>-96.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-96.2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-96.3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-96.4</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-96.1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-96.2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-96.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-96.3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-96.4</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-96.1</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-96.1</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-95.4</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-96.1</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-95.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-96</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-95.7</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-95.8</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-95.9</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-96.1</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-95.4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-95.6</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-96</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-95.8</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-95.7</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-95.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5536-4502-B358-B0DC477D42DE}"/>
+              <c16:uniqueId val="{00000003-7A63-40CE-9546-36EAC15F35EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5932,7 +5103,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="it-IT"/>
@@ -6050,7 +5221,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CAB04A61-326A-47D0-B92F-BE03751AB6FE}" type="CELLRANGE">
+                    <a:fld id="{75ADA4D9-907C-4AAB-B32C-E959CC22082C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6089,7 +5260,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{01CE87AC-A483-45B0-AEB2-BB955970B1AC}" type="CELLRANGE">
+                    <a:fld id="{524E7E99-1C5F-46FE-8932-5017275FF7DB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6128,7 +5299,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC5B4178-5E21-4F51-BC0C-591AEAF03605}" type="CELLRANGE">
+                    <a:fld id="{C4793FAC-5432-4352-BB71-F49690A6A05F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6167,7 +5338,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{63198700-E4B2-4C24-BC4A-2529E30FCE49}" type="CELLRANGE">
+                    <a:fld id="{F3CAAB52-924A-4E2B-B3C6-7AB400D50842}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6206,7 +5377,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E50C7467-A245-43B2-BE12-2B57817026BF}" type="CELLRANGE">
+                    <a:fld id="{B5C6777E-561A-4F65-82FF-DC2ED372ED2C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6245,7 +5416,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{510D36DB-C473-44EB-9B8F-C439F4009D88}" type="CELLRANGE">
+                    <a:fld id="{34F50427-180B-4DF0-BAA0-E9F03A9DEEBB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6284,7 +5455,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A0E6DB8D-EC98-455D-A666-D91F083B6CAF}" type="CELLRANGE">
+                    <a:fld id="{528FBDA0-2108-40DB-84E2-E612629B093B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6323,7 +5494,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{98827A90-8DAB-4C25-BC28-69C347288AE1}" type="CELLRANGE">
+                    <a:fld id="{EAFF8004-B1D6-4574-8C4F-00D90F22518A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6362,7 +5533,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BAD60AD1-283F-45BB-A2C6-EFF4A680E335}" type="CELLRANGE">
+                    <a:fld id="{F516ED58-AFC9-4C83-9124-8C568C19AF71}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6401,7 +5572,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EA290E73-C139-48DA-B816-70311CF7533F}" type="CELLRANGE">
+                    <a:fld id="{27079CDF-4D47-4A8E-A268-64B07E03F607}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6440,7 +5611,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ED003AD1-8AA7-4BEB-A690-6A1E6FE6AA1D}" type="CELLRANGE">
+                    <a:fld id="{F1981085-3AED-4A2A-B931-234E559B1FF9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6479,7 +5650,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{84827834-001C-47E9-B808-F2B9C518A105}" type="CELLRANGE">
+                    <a:fld id="{0F11DFED-6A3A-4D40-9F39-77DF87D40B20}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6518,7 +5689,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BCBAF345-ADB9-4ED0-8770-21C7A2C2F31B}" type="CELLRANGE">
+                    <a:fld id="{9747A858-3E08-4272-B1B9-1B63EB643775}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6557,7 +5728,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C653F0DB-50D0-42C3-99D0-48B2BE1DECCF}" type="CELLRANGE">
+                    <a:fld id="{70A5C5C9-97DB-45DD-9C4E-08CE6818B5E9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6596,7 +5767,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5614454C-A62B-4537-B297-C95FF4C334A7}" type="CELLRANGE">
+                    <a:fld id="{E26AEEAD-283E-49B2-A397-CA4999421F64}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6635,7 +5806,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA46F4D0-6BEB-4E6F-9976-87783D7129F6}" type="CELLRANGE">
+                    <a:fld id="{15785D0C-DD60-4855-A32F-E167AA42F22E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6674,7 +5845,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0C937A9C-2358-4C62-A870-330C2CC47AAC}" type="CELLRANGE">
+                    <a:fld id="{EE3D5B48-01B7-4A6A-8F0B-2CA23343F647}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6713,7 +5884,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{92FD0BDC-788C-4A16-97B2-C051050F8407}" type="CELLRANGE">
+                    <a:fld id="{FBAF3040-4021-4C13-8C07-442AFCCB0F85}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6752,7 +5923,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D42A8CF6-A1FB-44AE-95D9-3530FAB55AE1}" type="CELLRANGE">
+                    <a:fld id="{79F1AC48-551F-45FD-A87F-CFCDE28AF85F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6791,7 +5962,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D77F3E7A-C6F3-412A-A10E-B277619A0856}" type="CELLRANGE">
+                    <a:fld id="{5E420B1A-2C59-4A48-A19B-B0D8FA83378C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6830,7 +6001,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{32A2A878-8C3B-4AE8-8AB7-73A50B77FC1E}" type="CELLRANGE">
+                    <a:fld id="{B13FEBF5-327B-438E-85FA-613A39933152}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6869,7 +6040,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{888EF562-F76E-49F6-BB4F-754533E3A690}" type="CELLRANGE">
+                    <a:fld id="{0B7C4597-9366-4959-A912-8555A8BE29CC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6908,7 +6079,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BBD623D6-6A39-41F2-B60F-FB20A8BD8A22}" type="CELLRANGE">
+                    <a:fld id="{B52D897A-8AB3-470E-BE7D-4A6FE6C8FB5F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6947,7 +6118,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E7EED383-907A-46ED-BA16-D5A053E5695C}" type="CELLRANGE">
+                    <a:fld id="{1DEAB9BD-3515-4B29-89C0-4DB160FB37D3}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -6986,7 +6157,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1644430A-64B3-44A3-982A-9C2D3C2B598C}" type="CELLRANGE">
+                    <a:fld id="{43BA05D6-3AC9-48F8-AEFC-9742942CC369}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7025,7 +6196,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9530C28B-8001-4DC9-A910-97DCEB2CE249}" type="CELLRANGE">
+                    <a:fld id="{348E5516-C9D6-446D-8788-4BD51755313C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7064,7 +6235,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B1BADC6F-A912-4D33-92DA-570410A06964}" type="CELLRANGE">
+                    <a:fld id="{D954B6DA-CE18-405B-B3C1-8C526C95E9AA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7103,7 +6274,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6FB61DC6-BF08-430A-8DE3-03B18BB2F404}" type="CELLRANGE">
+                    <a:fld id="{E2E0C650-115B-41A0-BEE6-100071B8AAC2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7142,7 +6313,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC92E9E9-BBD2-4169-99A4-88CC4A9F76DB}" type="CELLRANGE">
+                    <a:fld id="{21FCF550-BC14-4011-A288-7EF895FF7460}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7181,7 +6352,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A85AFD5B-BD45-4098-99BE-F9F539D10FD9}" type="CELLRANGE">
+                    <a:fld id="{4FDF2015-DA91-4653-B58F-28C640D36874}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7220,7 +6391,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D56AFD0B-D3FA-4451-BE77-BC66948C6E84}" type="CELLRANGE">
+                    <a:fld id="{B10BFD3D-7B01-4B31-9846-9B2F02C26244}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7259,7 +6430,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A7BD3846-BA76-49B9-A1E6-7E3B9FBFB9E1}" type="CELLRANGE">
+                    <a:fld id="{D5B25B4A-E122-43D9-8A74-FF538C1F45A6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7298,7 +6469,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B08F937-4AAD-48F9-8BF3-FB7AC97C18A7}" type="CELLRANGE">
+                    <a:fld id="{96B7F598-2A5E-438E-8A54-FE70A36133FF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7337,7 +6508,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B2058ACB-62FB-4F40-BB85-DB645E720C7B}" type="CELLRANGE">
+                    <a:fld id="{0576D6E3-EC2C-4421-8EB3-584C9BC93A8B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7376,7 +6547,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{17C62D20-AEBB-4671-BD59-CC52B8E70B07}" type="CELLRANGE">
+                    <a:fld id="{41F2084C-A05A-4F32-BB4D-B8146F034689}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7415,7 +6586,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B94F1B5A-B2E8-4555-B21A-234DEB3E28B1}" type="CELLRANGE">
+                    <a:fld id="{06C85B95-5076-464A-9C0C-D1D901795B12}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7454,7 +6625,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C6D066DB-DA27-483D-A0AF-2F9EEF36B340}" type="CELLRANGE">
+                    <a:fld id="{D444EA3F-9D05-4B03-8718-382F0EA66425}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7493,7 +6664,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0F51DA66-BC09-482D-9B4C-FA90D49763E0}" type="CELLRANGE">
+                    <a:fld id="{5454734A-20AE-4EF3-B58A-C8A723184C2D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7532,7 +6703,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CDFFA896-78BB-4AF7-98C6-B20B0DE52AFD}" type="CELLRANGE">
+                    <a:fld id="{4A05CE75-248D-44AD-B3CA-DA3CCD7725F7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7571,7 +6742,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6BE56EBC-1432-45F8-AFFE-7FD58F59E88D}" type="CELLRANGE">
+                    <a:fld id="{408174B5-F309-4238-A0AD-65C091230548}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7610,7 +6781,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{31F3B68B-B126-4AF4-AD74-174A4D321FD3}" type="CELLRANGE">
+                    <a:fld id="{79A73BED-7ED4-4124-BE04-2E12B8440223}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -7649,7 +6820,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F4D83017-1B4A-403B-9C59-C8513A17AAA8}" type="CELLRANGE">
+                    <a:fld id="{CD6007DD-BCDE-43A3-88F2-F935BC95A63F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[INTERVALLOCELLE]</a:t>
@@ -8408,7 +7579,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="it-IT"/>
@@ -10183,7 +9354,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="it-IT"/>
@@ -11337,14 +10508,48 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
-  <a:schemeClr val="accent5"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+  <a:schemeClr val="accent3"/>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -11389,46 +10594,6 @@
 </file>
 
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12517,502 +11682,6 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13536,7 +12205,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14052,7 +12721,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14577,7 +13246,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15168,57 +13837,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>625489</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>106486</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1967230</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>135890</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1915648</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>5793</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Grafico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D907407F-7AA4-DCB7-B04A-D44293E4E0F5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>595630</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1270</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>599440</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>80010</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15246,7 +13874,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -15287,7 +13915,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -15733,56 +14361,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giordana" refreshedDate="46075.624658333334" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{B1988D9F-E421-4449-AAF3-6C918CB1BCDC}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="B1:C61" sheet="Performances"/>
-  </cacheSource>
-  <cacheFields count="2">
-    <cacheField name="Dipartimento" numFmtId="0">
-      <sharedItems count="5">
-        <s v="Vendite"/>
-        <s v="Risorse Umane"/>
-        <s v="IT"/>
-        <s v="Finanza"/>
-        <s v="Marketing"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Valutazione delle Prestazioni" numFmtId="166">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.3" maxValue="4.9000000000000004" count="17">
-        <n v="4.5"/>
-        <n v="3.8"/>
-        <n v="4.2"/>
-        <n v="4.8"/>
-        <n v="3.5"/>
-        <n v="4"/>
-        <n v="3.7"/>
-        <n v="3.9"/>
-        <n v="4.3"/>
-        <n v="3.6"/>
-        <n v="4.0999999999999996"/>
-        <n v="4.7"/>
-        <n v="3.4"/>
-        <n v="4.4000000000000004"/>
-        <n v="4.5999999999999996"/>
-        <n v="4.9000000000000004"/>
-        <n v="3.3"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giordana" refreshedDate="46075.634478356478" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{CE180FDC-92DB-43A2-A617-A08CA86557AA}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D61" sheet="Performances"/>
   </cacheSource>
-  <cacheFields count="4">
+  <cacheFields count="7">
     <cacheField name="Codice Dipendente" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="101" maxValue="160" count="60">
         <n v="101"/>
@@ -15880,6 +14463,9 @@
     <cacheField name="Valutazione dell'Anno Precedente" numFmtId="166">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1" maxValue="4.5999999999999996"/>
     </cacheField>
+    <cacheField name="Campo1" numFmtId="0" formula=" 0" databaseField="0"/>
+    <cacheField name="Differenza performance rispetto anno precedente" numFmtId="0" formula=" 0" databaseField="0"/>
+    <cacheField name="Diff.Performance rispetto anno precedente" numFmtId="0" formula="'Valutazione delle Prestazioni' -'Valutazione dell''Anno Precedente' /'Valutazione dell''Anno Precedente' *100" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -15889,7 +14475,7 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giordana" refreshedDate="46076.517405902778" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="42" xr:uid="{7996D084-7CC2-4A01-9EC0-2BBCAD3EC7F2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:K43" sheet="Social Media Categoria"/>
@@ -16462,251 +15048,6 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="6"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="15"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="16"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="9"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="3"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="5"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="8"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="10"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="11"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="12"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="7"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="13"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="14"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="9"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
-  <r>
-    <x v="0"/>
-    <x v="0"/>
     <x v="0"/>
     <n v="4.2"/>
   </r>
@@ -17067,7 +15408,7 @@
 </pivotCacheRecords>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="42">
   <r>
     <x v="0"/>
@@ -17619,7 +15960,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0134461-C2FA-400A-AF6E-33C6FB2797B5}" name="Tabella pivot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E0134461-C2FA-400A-AF6E-33C6FB2797B5}" name="Tabella pivot1" cacheId="80" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:L12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -17722,13 +16063,13 @@
     <dataField name="Somma di VENDITE" fld="2" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="33">
+    <format dxfId="10">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="9">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1">
@@ -17740,7 +16081,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -17888,7 +16229,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F318C7A7-1CC3-4CF6-B9B2-D8E92F1910C2}" name="Tabella pivot2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F318C7A7-1CC3-4CF6-B9B2-D8E92F1910C2}" name="Tabella pivot2" cacheId="80" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B81" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -18199,98 +16540,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8CDE92AC-A28B-411F-8C19-EAA4A73596BB}" name="Tabella pivot42" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="166" showAll="0">
-      <items count="18">
-        <item x="16"/>
-        <item x="12"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="14"/>
-        <item x="11"/>
-        <item x="3"/>
-        <item x="15"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Media di Valutazione delle Prestazioni" fld="1" subtotal="average" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5B5DF2A-5CD3-441A-B54E-D2785344E2C2}" name="Tabella pivot44" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5B5DF2A-5CD3-441A-B54E-D2785344E2C2}" name="Tabella pivot44" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A3:B69" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0">
       <items count="61">
         <item x="0"/>
@@ -18356,7 +16608,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+    <pivotField axis="axisRow" showAll="0">
       <items count="6">
         <item x="3"/>
         <item x="2"/>
@@ -18366,14 +16618,17 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
     <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="40">
+  <rowItems count="66">
     <i>
       <x/>
     </i>
@@ -18453,6 +16708,84 @@
       <x v="57"/>
     </i>
     <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+    </i>
+    <i r="1">
+      <x v="54"/>
+    </i>
+    <i r="1">
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+    </i>
+    <i r="1">
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+    </i>
+    <i r="1">
+      <x v="56"/>
+    </i>
+    <i>
       <x v="4"/>
     </i>
     <i r="1">
@@ -18499,10 +16832,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Media di Valutazione delle Prestazioni" fld="2" subtotal="average" baseField="1" baseItem="0" numFmtId="166"/>
+    <dataField name="Somma di Diff.Performance rispetto anno precedente" fld="6" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="0" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -18513,17 +16846,6 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="1" type="valueGreaterThan" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <customFilters>
-            <customFilter operator="greaterThan" val="4"/>
-          </customFilters>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -18535,8 +16857,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238417CE-9BA7-4F76-8628-73D2F51DD7DF}" name="Tabella pivot4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{238417CE-9BA7-4F76-8628-73D2F51DD7DF}" name="Tabella pivot4" cacheId="82" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:E14" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField axis="axisRow" showAll="0">
@@ -18704,7 +17026,7 @@
     <dataField name="Somma di Commenti" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="6">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -19190,15 +17512,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{566DE3A5-62A5-44D1-9653-58843D4C57EA}" name="Tabella1" displayName="Tabella1" ref="A1:C87" totalsRowShown="0" headerRowDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{566DE3A5-62A5-44D1-9653-58843D4C57EA}" name="Tabella1" displayName="Tabella1" ref="A1:C87" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A1:C87" xr:uid="{566DE3A5-62A5-44D1-9653-58843D4C57EA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C87">
     <sortCondition descending="1" ref="C2:C87"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E16EBBCE-889C-4537-B9B6-B565FEC26FAC}" name="CATEGORIA PRODOTTO" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{1AE8705B-466F-4BC5-8A20-2F2AD27588A7}" name="PUNTO VENDITA" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{C7917BBD-FF44-4009-8897-741010108AD0}" name="VENDITE" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{E16EBBCE-889C-4537-B9B6-B565FEC26FAC}" name="CATEGORIA PRODOTTO" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1AE8705B-466F-4BC5-8A20-2F2AD27588A7}" name="PUNTO VENDITA" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{C7917BBD-FF44-4009-8897-741010108AD0}" name="VENDITE" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -48287,7 +46609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
@@ -48297,7 +46619,7 @@
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.6640625" customWidth="1"/>
+    <col min="5" max="5" width="46.88671875" customWidth="1"/>
     <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.44140625" customWidth="1"/>
   </cols>
@@ -48316,7 +46638,7 @@
         <v>23</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -48339,7 +46661,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20">
         <v>102</v>
       </c>
@@ -48393,7 +46715,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20">
         <v>105</v>
       </c>
@@ -48411,7 +46733,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20">
         <v>106</v>
       </c>
@@ -48429,7 +46751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>107</v>
       </c>
@@ -48483,7 +46805,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20">
         <v>110</v>
       </c>
@@ -48519,7 +46841,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20">
         <v>112</v>
       </c>
@@ -48537,7 +46859,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
         <v>113</v>
       </c>
@@ -48573,7 +46895,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>115</v>
       </c>
@@ -48609,7 +46931,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20">
         <v>117</v>
       </c>
@@ -48663,7 +46985,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>120</v>
       </c>
@@ -48681,7 +47003,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20">
         <v>121</v>
       </c>
@@ -48699,7 +47021,7 @@
         <v>3.0999999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
         <v>122</v>
       </c>
@@ -48753,7 +47075,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20">
         <v>125</v>
       </c>
@@ -48771,7 +47093,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20">
         <v>126</v>
       </c>
@@ -48789,7 +47111,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>127</v>
       </c>
@@ -48807,7 +47129,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20">
         <v>128</v>
       </c>
@@ -48843,7 +47165,7 @@
         <v>3.4000000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
         <v>130</v>
       </c>
@@ -48879,7 +47201,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20">
         <v>132</v>
       </c>
@@ -48933,7 +47255,7 @@
         <v>3.9000000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20">
         <v>135</v>
       </c>
@@ -48969,7 +47291,7 @@
         <v>3.4000000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20">
         <v>137</v>
       </c>
@@ -49023,7 +47345,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20">
         <v>140</v>
       </c>
@@ -49041,7 +47363,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20">
         <v>141</v>
       </c>
@@ -49059,7 +47381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20">
         <v>142</v>
       </c>
@@ -49077,7 +47399,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20">
         <v>143</v>
       </c>
@@ -49113,7 +47435,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20">
         <v>145</v>
       </c>
@@ -49149,7 +47471,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20">
         <v>147</v>
       </c>
@@ -49203,7 +47525,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20">
         <v>150</v>
       </c>
@@ -49239,7 +47561,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20">
         <v>152</v>
       </c>
@@ -49257,7 +47579,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20">
         <v>153</v>
       </c>
@@ -49293,7 +47615,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="20">
         <v>155</v>
       </c>
@@ -49329,7 +47651,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20">
         <v>157</v>
       </c>
@@ -49383,7 +47705,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20">
         <v>160</v>
       </c>
@@ -49402,19 +47724,26 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D61" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:D61" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="4"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F352A0FE-A64A-406E-9944-E363F2DE95BA}">
-  <dimension ref="A3:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC82A2B5-4C77-4602-80AC-CA6012B61998}">
+  <dimension ref="A3:B69"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -49422,7 +47751,7 @@
         <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -49430,47 +47759,527 @@
         <v>27</v>
       </c>
       <c r="B4" s="19">
-        <v>4.5916666666666668</v>
+        <v>-44.9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="16">
+        <v>104</v>
+      </c>
+      <c r="B5" s="19">
+        <v>-95.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
+        <v>109</v>
+      </c>
+      <c r="B6" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
+        <v>114</v>
+      </c>
+      <c r="B7" s="19">
+        <v>-95.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
+        <v>119</v>
+      </c>
+      <c r="B8" s="19">
+        <v>-95.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>124</v>
+      </c>
+      <c r="B9" s="19">
+        <v>-95.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
+        <v>129</v>
+      </c>
+      <c r="B10" s="19">
+        <v>-95.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
+        <v>134</v>
+      </c>
+      <c r="B11" s="19">
+        <v>-95.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
+        <v>139</v>
+      </c>
+      <c r="B12" s="19">
+        <v>-95.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
+        <v>144</v>
+      </c>
+      <c r="B13" s="19">
+        <v>-95.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
+        <v>149</v>
+      </c>
+      <c r="B14" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
+        <v>154</v>
+      </c>
+      <c r="B15" s="19">
+        <v>-95.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
+        <v>159</v>
+      </c>
+      <c r="B16" s="19">
+        <v>-95.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="19">
-        <v>4.2583333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="B17" s="19">
+        <v>-48.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
+        <v>103</v>
+      </c>
+      <c r="B18" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="16">
+        <v>108</v>
+      </c>
+      <c r="B19" s="19">
+        <v>-95.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="16">
+        <v>113</v>
+      </c>
+      <c r="B20" s="19">
+        <v>-95.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
+        <v>118</v>
+      </c>
+      <c r="B21" s="19">
+        <v>-95.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
+        <v>123</v>
+      </c>
+      <c r="B22" s="19">
+        <v>-95.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
+        <v>128</v>
+      </c>
+      <c r="B23" s="19">
+        <v>-96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
+        <v>133</v>
+      </c>
+      <c r="B24" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
+        <v>138</v>
+      </c>
+      <c r="B25" s="19">
+        <v>-95.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
+        <v>143</v>
+      </c>
+      <c r="B26" s="19">
+        <v>-95.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
+        <v>148</v>
+      </c>
+      <c r="B27" s="19">
+        <v>-95.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
+        <v>153</v>
+      </c>
+      <c r="B28" s="19">
+        <v>-95.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="16">
+        <v>158</v>
+      </c>
+      <c r="B29" s="19">
+        <v>-95.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="19">
-        <v>3.5749999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="B30" s="19">
+        <v>-57.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <v>105</v>
+      </c>
+      <c r="B31" s="19">
+        <v>-96.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="16">
+        <v>110</v>
+      </c>
+      <c r="B32" s="19">
+        <v>-96.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="16">
+        <v>115</v>
+      </c>
+      <c r="B33" s="19">
+        <v>-96.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="16">
+        <v>120</v>
+      </c>
+      <c r="B34" s="19">
+        <v>-96.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="16">
+        <v>125</v>
+      </c>
+      <c r="B35" s="19">
+        <v>-96.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="16">
+        <v>130</v>
+      </c>
+      <c r="B36" s="19">
+        <v>-96.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="16">
+        <v>135</v>
+      </c>
+      <c r="B37" s="19">
+        <v>-96.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="16">
+        <v>140</v>
+      </c>
+      <c r="B38" s="19">
+        <v>-96.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="16">
+        <v>145</v>
+      </c>
+      <c r="B39" s="19">
+        <v>-96.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
+        <v>150</v>
+      </c>
+      <c r="B40" s="19">
+        <v>-96.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="16">
+        <v>155</v>
+      </c>
+      <c r="B41" s="19">
+        <v>-96.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="16">
+        <v>160</v>
+      </c>
+      <c r="B42" s="19">
+        <v>-96.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="19">
-        <v>3.8249999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="B43" s="19">
+        <v>-54.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="16">
+        <v>102</v>
+      </c>
+      <c r="B44" s="19">
+        <v>-96.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="16">
+        <v>107</v>
+      </c>
+      <c r="B45" s="19">
+        <v>-96.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="16">
+        <v>112</v>
+      </c>
+      <c r="B46" s="19">
+        <v>-96.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="16">
+        <v>117</v>
+      </c>
+      <c r="B47" s="19">
+        <v>-96.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="16">
+        <v>122</v>
+      </c>
+      <c r="B48" s="19">
+        <v>-96.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="16">
+        <v>127</v>
+      </c>
+      <c r="B49" s="19">
+        <v>-96.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="16">
+        <v>132</v>
+      </c>
+      <c r="B50" s="19">
+        <v>-96.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="16">
+        <v>137</v>
+      </c>
+      <c r="B51" s="19">
+        <v>-96.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="16">
+        <v>142</v>
+      </c>
+      <c r="B52" s="19">
+        <v>-96.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="16">
+        <v>147</v>
+      </c>
+      <c r="B53" s="19">
+        <v>-96.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="16">
+        <v>152</v>
+      </c>
+      <c r="B54" s="19">
+        <v>-95.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="16">
+        <v>157</v>
+      </c>
+      <c r="B55" s="19">
+        <v>-96.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="19">
-        <v>4.2250000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="B56" s="19">
+        <v>-49.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="16">
+        <v>101</v>
+      </c>
+      <c r="B57" s="19">
+        <v>-95.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="16">
+        <v>106</v>
+      </c>
+      <c r="B58" s="19">
+        <v>-96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="16">
+        <v>111</v>
+      </c>
+      <c r="B59" s="19">
+        <v>-95.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="16">
+        <v>116</v>
+      </c>
+      <c r="B60" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="16">
         <v>121</v>
       </c>
-      <c r="B9" s="19">
-        <v>4.0950000000000006</v>
+      <c r="B61" s="19">
+        <v>-95.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="16">
+        <v>126</v>
+      </c>
+      <c r="B62" s="19">
+        <v>-96.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="16">
+        <v>131</v>
+      </c>
+      <c r="B63" s="19">
+        <v>-95.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="16">
+        <v>136</v>
+      </c>
+      <c r="B64" s="19">
+        <v>-95.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="16">
+        <v>141</v>
+      </c>
+      <c r="B65" s="19">
+        <v>-96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="16">
+        <v>146</v>
+      </c>
+      <c r="B66" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="16">
+        <v>151</v>
+      </c>
+      <c r="B67" s="19">
+        <v>-95.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="16">
+        <v>156</v>
+      </c>
+      <c r="B68" s="19">
+        <v>-95.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B69" s="19">
+        <v>145.70000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -49480,349 +48289,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC82A2B5-4C77-4602-80AC-CA6012B61998}">
-  <dimension ref="A3:B43"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="19">
-        <v>4.5916666666666668</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="16">
-        <v>104</v>
-      </c>
-      <c r="B5" s="19">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
-        <v>109</v>
-      </c>
-      <c r="B6" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
-        <v>114</v>
-      </c>
-      <c r="B7" s="19">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
-        <v>119</v>
-      </c>
-      <c r="B8" s="19">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
-        <v>124</v>
-      </c>
-      <c r="B9" s="19">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
-        <v>129</v>
-      </c>
-      <c r="B10" s="19">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
-        <v>134</v>
-      </c>
-      <c r="B11" s="19">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="16">
-        <v>139</v>
-      </c>
-      <c r="B12" s="19">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
-        <v>144</v>
-      </c>
-      <c r="B13" s="19">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <v>149</v>
-      </c>
-      <c r="B14" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
-        <v>154</v>
-      </c>
-      <c r="B15" s="19">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
-        <v>159</v>
-      </c>
-      <c r="B16" s="19">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="19">
-        <v>4.2583333333333337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="16">
-        <v>103</v>
-      </c>
-      <c r="B18" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="16">
-        <v>108</v>
-      </c>
-      <c r="B19" s="19">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
-        <v>113</v>
-      </c>
-      <c r="B20" s="19">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
-        <v>118</v>
-      </c>
-      <c r="B21" s="19">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="16">
-        <v>123</v>
-      </c>
-      <c r="B22" s="19">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
-        <v>128</v>
-      </c>
-      <c r="B23" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>133</v>
-      </c>
-      <c r="B24" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="16">
-        <v>138</v>
-      </c>
-      <c r="B25" s="19">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
-        <v>143</v>
-      </c>
-      <c r="B26" s="19">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
-        <v>148</v>
-      </c>
-      <c r="B27" s="19">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
-        <v>153</v>
-      </c>
-      <c r="B28" s="19">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
-        <v>158</v>
-      </c>
-      <c r="B29" s="19">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="19">
-        <v>4.2250000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
-        <v>101</v>
-      </c>
-      <c r="B31" s="19">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
-        <v>106</v>
-      </c>
-      <c r="B32" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="16">
-        <v>111</v>
-      </c>
-      <c r="B33" s="19">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="16">
-        <v>116</v>
-      </c>
-      <c r="B34" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
-        <v>121</v>
-      </c>
-      <c r="B35" s="19">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="16">
-        <v>126</v>
-      </c>
-      <c r="B36" s="19">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="16">
-        <v>131</v>
-      </c>
-      <c r="B37" s="19">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="16">
-        <v>136</v>
-      </c>
-      <c r="B38" s="19">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="16">
-        <v>141</v>
-      </c>
-      <c r="B39" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="16">
-        <v>146</v>
-      </c>
-      <c r="B40" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="16">
-        <v>151</v>
-      </c>
-      <c r="B41" s="19">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="16">
-        <v>156</v>
-      </c>
-      <c r="B42" s="19">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B43" s="19">
-        <v>4.3583333333333325</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -49865,19 +48331,19 @@
         <v>35</v>
       </c>
       <c r="H1" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I1" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="J1" s="30" t="s">
         <v>126</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>127</v>
       </c>
       <c r="M1" s="23" t="s">
         <v>29</v>
       </c>
       <c r="N1" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.3">
@@ -60155,24 +58621,24 @@
   </sortState>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A2:J43">
-    <cfRule type="expression" dxfId="29" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$A2="PetWhisperer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$A2="AdventureJunkie"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>$A2="FitnessFanatic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N43">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$A2="PetWhisperer"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$A2="AdventureJunkie"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$A2="FitnessFanatic"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60181,7 +58647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA11E167-F34F-4994-A12B-C97BC427EA84}">
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -60201,7 +58667,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1" s="36" t="s">
         <v>30</v>
@@ -60222,13 +58688,13 @@
         <v>35</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J1" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>126</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -60236,7 +58702,7 @@
         <v>92</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C2" s="38" t="s">
         <v>115</v>
@@ -60274,7 +58740,7 @@
         <v>46</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>47</v>
@@ -60312,7 +58778,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>49</v>
@@ -60350,7 +58816,7 @@
         <v>44</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>45</v>
@@ -60388,7 +58854,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>80</v>
@@ -60426,7 +58892,7 @@
         <v>36</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>37</v>
@@ -60464,7 +58930,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>53</v>
@@ -60502,7 +58968,7 @@
         <v>77</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>78</v>
@@ -60540,7 +59006,7 @@
         <v>65</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>66</v>
@@ -60578,7 +59044,7 @@
         <v>42</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>43</v>
@@ -60616,7 +59082,7 @@
         <v>59</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>60</v>
@@ -60654,7 +59120,7 @@
         <v>63</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>64</v>
@@ -60692,7 +59158,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>51</v>
@@ -60730,7 +59196,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>39</v>
@@ -60768,7 +59234,7 @@
         <v>56</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>57</v>
@@ -60806,7 +59272,7 @@
         <v>108</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>109</v>
@@ -60844,7 +59310,7 @@
         <v>93</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>116</v>
@@ -60882,7 +59348,7 @@
         <v>40</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>41</v>
@@ -60920,7 +59386,7 @@
         <v>102</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>119</v>
@@ -60958,7 +59424,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>84</v>
@@ -60996,7 +59462,7 @@
         <v>70</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>71</v>
@@ -61034,7 +59500,7 @@
         <v>68</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>69</v>
@@ -61072,7 +59538,7 @@
         <v>103</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>104</v>
@@ -61110,7 +59576,7 @@
         <v>61</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>62</v>
@@ -61148,7 +59614,7 @@
         <v>96</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>117</v>
@@ -61186,7 +59652,7 @@
         <v>85</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>86</v>
@@ -61224,7 +59690,7 @@
         <v>88</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>89</v>
@@ -61262,7 +59728,7 @@
         <v>81</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C29" s="38" t="s">
         <v>82</v>
@@ -61300,7 +59766,7 @@
         <v>73</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C30" s="38" t="s">
         <v>74</v>
@@ -61338,7 +59804,7 @@
         <v>110</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C31" s="38" t="s">
         <v>111</v>
@@ -61376,7 +59842,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="38" t="s">
         <v>95</v>
@@ -61414,7 +59880,7 @@
         <v>101</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C33" s="38" t="s">
         <v>118</v>
@@ -61452,7 +59918,7 @@
         <v>90</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C34" s="38" t="s">
         <v>91</v>
@@ -61490,7 +59956,7 @@
         <v>105</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C35" s="38" t="s">
         <v>106</v>
@@ -61528,7 +59994,7 @@
         <v>54</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C36" s="38" t="s">
         <v>55</v>
@@ -61566,7 +60032,7 @@
         <v>75</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>107</v>
@@ -61604,7 +60070,7 @@
         <v>76</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>112</v>
@@ -61642,7 +60108,7 @@
         <v>58</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>113</v>
@@ -61680,7 +60146,7 @@
         <v>72</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>97</v>
@@ -61718,7 +60184,7 @@
         <v>87</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>114</v>
@@ -61756,7 +60222,7 @@
         <v>98</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C42" s="38" t="s">
         <v>99</v>
@@ -61794,7 +60260,7 @@
         <v>67</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C43" s="38" t="s">
         <v>100</v>
@@ -61832,7 +60298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3DF056-FE54-4C3F-BBCC-72728F21BA31}">
   <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -61865,14 +60331,14 @@
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="42"/>
       <c r="B4" s="42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="42" t="s">
         <v>130</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -61880,10 +60346,10 @@
         <v>120</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -61892,16 +60358,16 @@
       <c r="A6" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="42">
         <v>400</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="42">
         <v>45</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="42">
         <v>400</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="42">
         <v>45</v>
       </c>
     </row>
@@ -61909,16 +60375,16 @@
       <c r="A7" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="42">
         <v>800</v>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="42">
         <v>70</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="42">
         <v>800</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="42">
         <v>70</v>
       </c>
     </row>
@@ -61926,16 +60392,16 @@
       <c r="A8" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="42">
         <v>750</v>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="42">
         <v>70</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="42">
         <v>750</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="42">
         <v>70</v>
       </c>
     </row>
@@ -61943,16 +60409,16 @@
       <c r="A9" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="42">
         <v>450</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="42">
         <v>40</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="42">
         <v>450</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="42">
         <v>40</v>
       </c>
     </row>
@@ -61960,16 +60426,16 @@
       <c r="A10" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="42">
         <v>900</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="42">
         <v>80</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="42">
         <v>900</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="42">
         <v>80</v>
       </c>
     </row>
@@ -61977,16 +60443,16 @@
       <c r="A11" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="42">
         <v>600</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="42">
         <v>55</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="42">
         <v>600</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="42">
         <v>55</v>
       </c>
     </row>
@@ -61994,16 +60460,16 @@
       <c r="A12" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="42">
         <v>550</v>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="42">
         <v>50</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="42">
         <v>550</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="42">
         <v>50</v>
       </c>
     </row>
@@ -62011,16 +60477,16 @@
       <c r="A13" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="42">
         <v>600</v>
       </c>
-      <c r="C13" s="45">
+      <c r="C13" s="42">
         <v>55</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="42">
         <v>600</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="42">
         <v>55</v>
       </c>
     </row>
@@ -62028,50 +60494,50 @@
       <c r="A14" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="42">
         <v>5050</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="42">
         <v>465</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="42">
         <v>5050</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="42">
         <v>465</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="24" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="31" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="32" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="22" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="24" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="25" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="31" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="32" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="37" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="38" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="40" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="41" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="42" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="43" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="44" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="45" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="46" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="48" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="50" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="51" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="52" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
